--- a/data/trans_orig/PCS12_SP_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2007</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147902</t>
+          <t>147094</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196327</t>
+          <t>194586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122691</t>
+          <t>123846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167732</t>
+          <t>169016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>285321</t>
+          <t>284290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354831</t>
+          <t>352099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190942</t>
+          <t>189675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243446</t>
+          <t>240597</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146145</t>
+          <t>145940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>191823</t>
+          <t>194442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350639</t>
+          <t>347843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420780</t>
+          <t>420602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>286715</t>
+          <t>286980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>343610</t>
+          <t>345833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>325052</t>
+          <t>323129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>388241</t>
+          <t>389404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>624606</t>
+          <t>629841</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>716512</t>
+          <t>714723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300418</t>
+          <t>302478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>358421</t>
+          <t>361658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>609290</t>
+          <t>603850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>678170</t>
+          <t>677323</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>929251</t>
+          <t>927379</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1022323</t>
+          <t>1022209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423290</t>
+          <t>421683</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>499153</t>
+          <t>495740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>359059</t>
+          <t>361182</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>427005</t>
+          <t>428138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>811065</t>
+          <t>806304</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>915165</t>
+          <t>910570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>614393</t>
+          <t>612985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>692158</t>
+          <t>691618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432082</t>
+          <t>433141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>504048</t>
+          <t>502050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1063584</t>
+          <t>1065273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1170452</t>
+          <t>1174516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401414</t>
+          <t>402345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472312</t>
+          <t>473479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>474022</t>
+          <t>475136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>545513</t>
+          <t>547204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>897518</t>
+          <t>895739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1000310</t>
+          <t>1002625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,56%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124248</t>
+          <t>122267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>170490</t>
+          <t>169657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>190521</t>
+          <t>189844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>245874</t>
+          <t>242407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>324217</t>
+          <t>327281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>398363</t>
+          <t>399022</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151799</t>
+          <t>150682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196875</t>
+          <t>193988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116475</t>
+          <t>118223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157384</t>
+          <t>161408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,47 +1921,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>33,88%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>307975</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>278673</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>339614</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>29,96%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>27,11%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>33,04%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>307975</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>276115</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>338603</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>29,96%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174241</t>
+          <t>177612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221796</t>
+          <t>224020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111954</t>
+          <t>110219</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>152927</t>
+          <t>149966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,47 +2034,47 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>329879</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>302883</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>362433</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
           <t>32,1%</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>329879</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>301077</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>360348</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116722</t>
+          <t>116014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160108</t>
+          <t>159173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>131656</t>
+          <t>130837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172996</t>
+          <t>171495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>260439</t>
+          <t>261881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318142</t>
+          <t>320413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56762</t>
+          <t>56852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44704</t>
+          <t>46754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75139</t>
+          <t>74577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81217</t>
+          <t>82659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122954</t>
+          <t>124404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>749427</t>
+          <t>750304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>850486</t>
+          <t>848608</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>632651</t>
+          <t>633440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>722382</t>
+          <t>722978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1407531</t>
+          <t>1410103</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1545783</t>
+          <t>1548560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1013663</t>
+          <t>1011915</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1120740</t>
+          <t>1121842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>720642</t>
+          <t>717740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>819468</t>
+          <t>812969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1760659</t>
+          <t>1757840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1908415</t>
+          <t>1907379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>843275</t>
+          <t>842215</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>945505</t>
+          <t>946530</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>961833</t>
+          <t>958919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1068566</t>
+          <t>1070628</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1826442</t>
+          <t>1833389</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1982955</t>
+          <t>1981908</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>479996</t>
+          <t>474454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>560644</t>
+          <t>560810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>865860</t>
+          <t>868738</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>971428</t>
+          <t>973390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1365870</t>
+          <t>1362956</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1505658</t>
+          <t>1504916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2012</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131785</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179081</t>
+          <t>177515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>109995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154569</t>
+          <t>154580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253109</t>
+          <t>255649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>318985</t>
+          <t>318798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165397</t>
+          <t>165106</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215813</t>
+          <t>214397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>191263</t>
+          <t>188290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250797</t>
+          <t>245035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>372924</t>
+          <t>370755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>446996</t>
+          <t>446850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>253573</t>
+          <t>251186</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>312207</t>
+          <t>311230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>256139</t>
+          <t>255492</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>317606</t>
+          <t>321526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>524161</t>
+          <t>528932</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>614427</t>
+          <t>614919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>317654</t>
+          <t>318618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384404</t>
+          <t>384488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>661603</t>
+          <t>663931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>736544</t>
+          <t>738197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1003107</t>
+          <t>1005314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1099750</t>
+          <t>1105154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>615511</t>
+          <t>617165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>703562</t>
+          <t>706507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>481709</t>
+          <t>482363</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>557281</t>
+          <t>558669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1125583</t>
+          <t>1125455</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1239447</t>
+          <t>1241539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>522549</t>
+          <t>516365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>600786</t>
+          <t>601843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>426142</t>
+          <t>424008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>501595</t>
+          <t>501142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>969897</t>
+          <t>970590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1080441</t>
+          <t>1076818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489197</t>
+          <t>489622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>570545</t>
+          <t>572746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446926</t>
+          <t>447126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520973</t>
+          <t>523914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>960230</t>
+          <t>965481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1073892</t>
+          <t>1078274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>188056</t>
+          <t>187482</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245589</t>
+          <t>244504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259237</t>
+          <t>254967</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324256</t>
+          <t>320748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>458663</t>
+          <t>461118</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>549159</t>
+          <t>548152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140415</t>
+          <t>139626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185539</t>
+          <t>185242</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,47 +4393,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>133809</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>113591</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>156079</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>29,18%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>133809</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>114820</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>154917</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>270338</t>
+          <t>264713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>327601</t>
+          <t>328095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>150443</t>
+          <t>149900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>195307</t>
+          <t>194370</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130485</t>
+          <t>128933</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171964</t>
+          <t>170091</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>290631</t>
+          <t>290529</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>354160</t>
+          <t>354418</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82709</t>
+          <t>80685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121532</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110616</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154190</t>
+          <t>150595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>204010</t>
+          <t>202797</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258586</t>
+          <t>260965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>33282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60219</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57685</t>
+          <t>57604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>71908</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111021</t>
+          <t>111056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925331</t>
+          <t>921784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1032840</t>
+          <t>1030162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>735198</t>
+          <t>738165</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>841850</t>
+          <t>834830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1692207</t>
+          <t>1692153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1835518</t>
+          <t>1840913</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>868385</t>
+          <t>865184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>971900</t>
+          <t>972926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>779184</t>
+          <t>777494</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>885851</t>
+          <t>885891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1678380</t>
+          <t>1673708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1830715</t>
+          <t>1828653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>857930</t>
+          <t>857830</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>963500</t>
+          <t>965860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>854519</t>
+          <t>850652</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>958872</t>
+          <t>954422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1740061</t>
+          <t>1733255</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1890617</t>
+          <t>1885983</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>565188</t>
+          <t>568040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>658719</t>
+          <t>658322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>975482</t>
+          <t>980236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1084477</t>
+          <t>1090559</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1575258</t>
+          <t>1575971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1715690</t>
+          <t>1715349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2016</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148010</t>
+          <t>149882</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193020</t>
+          <t>195506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127422</t>
+          <t>130007</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174465</t>
+          <t>173323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>289783</t>
+          <t>290224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>353902</t>
+          <t>354055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97733</t>
+          <t>96796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135348</t>
+          <t>136992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94554</t>
+          <t>94043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135756</t>
+          <t>135126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201706</t>
+          <t>203337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255999</t>
+          <t>259206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>173528</t>
+          <t>172339</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>220034</t>
+          <t>219501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>195488</t>
+          <t>198773</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248857</t>
+          <t>250865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>382389</t>
+          <t>383220</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>456431</t>
+          <t>458152</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245010</t>
+          <t>247873</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>296839</t>
+          <t>301683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>474406</t>
+          <t>474024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>540171</t>
+          <t>541352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>736660</t>
+          <t>734966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>820669</t>
+          <t>820981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>757636</t>
+          <t>760127</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>844807</t>
+          <t>847154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>657425</t>
+          <t>655146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>737020</t>
+          <t>742892</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1440317</t>
+          <t>1437355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1561596</t>
+          <t>1562369</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>497593</t>
+          <t>497197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>578927</t>
+          <t>573760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>451640</t>
+          <t>448744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>529695</t>
+          <t>527771</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>973428</t>
+          <t>972273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1083305</t>
+          <t>1086471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451530</t>
+          <t>451909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528772</t>
+          <t>531454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>415979</t>
+          <t>416481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>489592</t>
+          <t>495846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>887511</t>
+          <t>890176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1002504</t>
+          <t>999055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218245</t>
+          <t>216865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274005</t>
+          <t>277288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>310869</t>
+          <t>314408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>383368</t>
+          <t>382995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>545687</t>
+          <t>550823</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>640185</t>
+          <t>643813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>209101</t>
+          <t>209751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>255819</t>
+          <t>261604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>175422</t>
+          <t>174184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>221101</t>
+          <t>222161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394372</t>
+          <t>400139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>463602</t>
+          <t>469152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145067</t>
+          <t>145975</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>189286</t>
+          <t>192224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>137894</t>
+          <t>139693</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182950</t>
+          <t>182946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>298195</t>
+          <t>298285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>360993</t>
+          <t>360127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81176</t>
+          <t>80494</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>118749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104584</t>
+          <t>103047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145264</t>
+          <t>141374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193000</t>
+          <t>194966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247136</t>
+          <t>248912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34169</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61397</t>
+          <t>64111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54426</t>
+          <t>53832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87616</t>
+          <t>87897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>95197</t>
+          <t>92624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142915</t>
+          <t>137182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1143121</t>
+          <t>1153296</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1263940</t>
+          <t>1263238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>991787</t>
+          <t>991373</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1102615</t>
+          <t>1100581</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2174863</t>
+          <t>2180665</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2335402</t>
+          <t>2344039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>771021</t>
+          <t>768037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>876945</t>
+          <t>871091</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>716702</t>
+          <t>720590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>813354</t>
+          <t>816688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1504970</t>
+          <t>1516489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1651265</t>
+          <t>1650988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>740709</t>
+          <t>737779</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>841160</t>
+          <t>837523</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>748297</t>
+          <t>746428</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>853509</t>
+          <t>852070</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1513319</t>
+          <t>1508122</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1654039</t>
+          <t>1655836</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>514660</t>
+          <t>523684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>607001</t>
+          <t>608559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>871445</t>
+          <t>865827</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>976704</t>
+          <t>978388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1418076</t>
+          <t>1422166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1562407</t>
+          <t>1556244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los cuartiles de la puntuación del componente de salud física (SF12) en 2023</t>
+          <t>Población según la puntuación, en cuartiles, del componente de salud física (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82788</t>
+          <t>82843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71757</t>
+          <t>71199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103287</t>
+          <t>104134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142469</t>
+          <t>143223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80471</t>
+          <t>81405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116059</t>
+          <t>116413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>79080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107002</t>
+          <t>107846</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168472</t>
+          <t>166496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214048</t>
+          <t>211367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100024</t>
+          <t>99496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135815</t>
+          <t>137003</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125449</t>
+          <t>127928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158707</t>
+          <t>158480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236003</t>
+          <t>235302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283895</t>
+          <t>285021</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>210442</t>
+          <t>207994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252184</t>
+          <t>251427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435797</t>
+          <t>433321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>477215</t>
+          <t>474699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>656676</t>
+          <t>656169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>715523</t>
+          <t>721062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>376315</t>
+          <t>376724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>630669</t>
+          <t>633755</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>363342</t>
+          <t>369092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>597769</t>
+          <t>586479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>854121</t>
+          <t>844851</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1169774</t>
+          <t>1193320</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>439367</t>
+          <t>433414</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>738243</t>
+          <t>732797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>447850</t>
+          <t>472030</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>758315</t>
+          <t>754887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1021645</t>
+          <t>1027563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1437302</t>
+          <t>1426576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316056</t>
+          <t>331054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>552476</t>
+          <t>555064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>492015</t>
+          <t>491792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1119595</t>
+          <t>1107664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>919526</t>
+          <t>943996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1634992</t>
+          <t>1703988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>406473</t>
+          <t>407640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1134287</t>
+          <t>1172065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>339150</t>
+          <t>336547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>529555</t>
+          <t>529266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>854580</t>
+          <t>852994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1807451</t>
+          <t>1632443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158336</t>
+          <t>159553</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216221</t>
+          <t>216737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184130</t>
+          <t>183214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>227631</t>
+          <t>225405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356658</t>
+          <t>355496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424062</t>
+          <t>425803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159407</t>
+          <t>159639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205670</t>
+          <t>206961</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163759</t>
+          <t>164129</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>205201</t>
+          <t>205544</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>337736</t>
+          <t>334587</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>401249</t>
+          <t>396545</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170133</t>
+          <t>168985</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>220706</t>
+          <t>218625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>147239</t>
+          <t>148456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185571</t>
+          <t>187239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330456</t>
+          <t>326862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>391359</t>
+          <t>390796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65900</t>
+          <t>66726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98714</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89493</t>
+          <t>88902</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120467</t>
+          <t>118685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163256</t>
+          <t>164064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207158</t>
+          <t>209578</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>617795</t>
+          <t>601888</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>881871</t>
+          <t>883964</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>626146</t>
+          <t>634640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>849235</t>
+          <t>843243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1358065</t>
+          <t>1349960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1694690</t>
+          <t>1694032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>719684</t>
+          <t>726991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1013458</t>
+          <t>1016495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>749965</t>
+          <t>738498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1044566</t>
+          <t>1029118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1576484</t>
+          <t>1578559</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2006017</t>
+          <t>1986923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>592477</t>
+          <t>634802</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>868486</t>
+          <t>871586</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>796372</t>
+          <t>798766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1578026</t>
+          <t>1474056</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1548668</t>
+          <t>1563118</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2292553</t>
+          <t>2398753</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>726030</t>
+          <t>727858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1550498</t>
+          <t>1516925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>835105</t>
+          <t>844777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1104369</t>
+          <t>1105800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1736497</t>
+          <t>1730995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2556680</t>
+          <t>2520879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147094</t>
+          <t>145695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>194586</t>
+          <t>195535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123846</t>
+          <t>124973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169016</t>
+          <t>172062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284290</t>
+          <t>281408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>352099</t>
+          <t>351218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189675</t>
+          <t>191003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>240597</t>
+          <t>242654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145940</t>
+          <t>147019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194442</t>
+          <t>194639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>347843</t>
+          <t>347983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420602</t>
+          <t>423765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>286980</t>
+          <t>287751</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>345833</t>
+          <t>344283</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>323129</t>
+          <t>321800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>389404</t>
+          <t>387379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>629841</t>
+          <t>629191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>714723</t>
+          <t>712223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>302478</t>
+          <t>303011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>361658</t>
+          <t>361221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>603850</t>
+          <t>608852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>677323</t>
+          <t>681078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>927379</t>
+          <t>931865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1022209</t>
+          <t>1022480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>421683</t>
+          <t>419932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>495740</t>
+          <t>496890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,47 +1317,47 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>24,8%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29,34%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>395324</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>361674</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>429811</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>24,9%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>395324</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>361182</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>428138</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>806304</t>
+          <t>806027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>910570</t>
+          <t>906773</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>612985</t>
+          <t>612501</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>691618</t>
+          <t>694007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>433141</t>
+          <t>431080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>502050</t>
+          <t>506230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1065273</t>
+          <t>1060615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1174516</t>
+          <t>1172651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402345</t>
+          <t>401457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473479</t>
+          <t>473049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>475136</t>
+          <t>473626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>547204</t>
+          <t>545335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895739</t>
+          <t>897015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1002625</t>
+          <t>997863</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122267</t>
+          <t>125837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169657</t>
+          <t>171736</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189844</t>
+          <t>188680</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242407</t>
+          <t>243637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327281</t>
+          <t>327538</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>399022</t>
+          <t>397094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150682</t>
+          <t>147810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193988</t>
+          <t>194149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118223</t>
+          <t>117044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>161408</t>
+          <t>157064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>278673</t>
+          <t>281062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>339614</t>
+          <t>342750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177612</t>
+          <t>176168</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>224020</t>
+          <t>224156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>110219</t>
+          <t>111373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149966</t>
+          <t>151925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>302883</t>
+          <t>300044</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>362433</t>
+          <t>361647</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116014</t>
+          <t>119440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159173</t>
+          <t>158160</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130837</t>
+          <t>131134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171495</t>
+          <t>172598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>261881</t>
+          <t>259210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320413</t>
+          <t>320941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30108</t>
+          <t>30343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56852</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46754</t>
+          <t>46298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74577</t>
+          <t>75491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82659</t>
+          <t>82964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124404</t>
+          <t>121905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>750304</t>
+          <t>756304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>848608</t>
+          <t>854936</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>633440</t>
+          <t>634319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>722978</t>
+          <t>727658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1410103</t>
+          <t>1410090</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1548560</t>
+          <t>1547192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1011915</t>
+          <t>1013832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1121842</t>
+          <t>1121247</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>717740</t>
+          <t>718870</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>812969</t>
+          <t>816034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1757840</t>
+          <t>1759492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1907379</t>
+          <t>1902877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>842215</t>
+          <t>841794</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>946530</t>
+          <t>941956</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>958919</t>
+          <t>961497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1070628</t>
+          <t>1067850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1833389</t>
+          <t>1831455</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1981908</t>
+          <t>1985114</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>474454</t>
+          <t>481030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>560810</t>
+          <t>562924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>868738</t>
+          <t>869194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>973390</t>
+          <t>978300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1362956</t>
+          <t>1371871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1504916</t>
+          <t>1505426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132585</t>
+          <t>131203</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177515</t>
+          <t>175261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109995</t>
+          <t>110939</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>155184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>255649</t>
+          <t>252903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>318798</t>
+          <t>320319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165106</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214397</t>
+          <t>213053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188290</t>
+          <t>193648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245035</t>
+          <t>248932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>370755</t>
+          <t>373945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>446850</t>
+          <t>443374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>251186</t>
+          <t>250624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311230</t>
+          <t>309564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255492</t>
+          <t>256670</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>321526</t>
+          <t>317384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>528932</t>
+          <t>523770</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>614919</t>
+          <t>612375</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318618</t>
+          <t>323758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>384488</t>
+          <t>385275</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>663931</t>
+          <t>663909</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>738197</t>
+          <t>738763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1005314</t>
+          <t>1003239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1105154</t>
+          <t>1100508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>617165</t>
+          <t>618393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>706507</t>
+          <t>705161</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>482363</t>
+          <t>480598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>558669</t>
+          <t>558809</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1125455</t>
+          <t>1123611</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1241539</t>
+          <t>1240727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>516365</t>
+          <t>520383</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>601843</t>
+          <t>603064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>424008</t>
+          <t>424299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>501142</t>
+          <t>502402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>970590</t>
+          <t>972833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1076818</t>
+          <t>1083813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489622</t>
+          <t>487272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>572746</t>
+          <t>572122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447126</t>
+          <t>444229</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>523914</t>
+          <t>520909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965481</t>
+          <t>951240</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078274</t>
+          <t>1065698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>187482</t>
+          <t>184885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244504</t>
+          <t>243573</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>254967</t>
+          <t>260505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320748</t>
+          <t>324214</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>461118</t>
+          <t>461239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>548152</t>
+          <t>549406</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139626</t>
+          <t>142202</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185242</t>
+          <t>187437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113591</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156079</t>
+          <t>153851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264713</t>
+          <t>264553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>328095</t>
+          <t>325986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>149900</t>
+          <t>151147</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194370</t>
+          <t>194598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128933</t>
+          <t>129753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>170091</t>
+          <t>170314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>290529</t>
+          <t>292028</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>354418</t>
+          <t>355212</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80685</t>
+          <t>82704</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118563</t>
+          <t>120828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110034</t>
+          <t>110674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150595</t>
+          <t>152748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202797</t>
+          <t>202703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>260965</t>
+          <t>261692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62688</t>
+          <t>62317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57604</t>
+          <t>58098</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71908</t>
+          <t>71318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111056</t>
+          <t>110576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>921784</t>
+          <t>924572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1030162</t>
+          <t>1032876</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>738165</t>
+          <t>736834</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>834830</t>
+          <t>834213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1692153</t>
+          <t>1688223</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1840913</t>
+          <t>1831328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>865184</t>
+          <t>866880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>972926</t>
+          <t>977389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>777494</t>
+          <t>778236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>885891</t>
+          <t>881403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1673708</t>
+          <t>1682708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1828653</t>
+          <t>1827299</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>857830</t>
+          <t>855016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>965860</t>
+          <t>964204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>850652</t>
+          <t>853827</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>954422</t>
+          <t>956517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1733255</t>
+          <t>1745045</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1885983</t>
+          <t>1895238</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>568040</t>
+          <t>565940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>658322</t>
+          <t>660424</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>980236</t>
+          <t>983118</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1090559</t>
+          <t>1088958</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1575971</t>
+          <t>1573601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1715349</t>
+          <t>1716594</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149882</t>
+          <t>149974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>195506</t>
+          <t>195053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130007</t>
+          <t>129773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173323</t>
+          <t>173450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>290224</t>
+          <t>288917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>354055</t>
+          <t>355029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96796</t>
+          <t>96350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136992</t>
+          <t>135717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94043</t>
+          <t>93273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135126</t>
+          <t>133012</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>203337</t>
+          <t>202981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259206</t>
+          <t>263576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172339</t>
+          <t>171093</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>219501</t>
+          <t>217366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198773</t>
+          <t>196629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>250865</t>
+          <t>250895</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>383220</t>
+          <t>383349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>458152</t>
+          <t>454979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>247873</t>
+          <t>248988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301683</t>
+          <t>298181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>474024</t>
+          <t>475542</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>541352</t>
+          <t>541964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>734966</t>
+          <t>736577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>820981</t>
+          <t>821002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>760127</t>
+          <t>758154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>847154</t>
+          <t>852138</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>655146</t>
+          <t>654443</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>742892</t>
+          <t>741066</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1437355</t>
+          <t>1441842</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1562369</t>
+          <t>1561975</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>497197</t>
+          <t>495952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>573760</t>
+          <t>578679</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>448744</t>
+          <t>453401</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>527771</t>
+          <t>531982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>972273</t>
+          <t>971189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1086471</t>
+          <t>1080496</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451909</t>
+          <t>453219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531454</t>
+          <t>534534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>416481</t>
+          <t>417854</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495846</t>
+          <t>492284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>890176</t>
+          <t>886077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>999055</t>
+          <t>999827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>216865</t>
+          <t>219563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>277288</t>
+          <t>278695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314408</t>
+          <t>310698</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>382995</t>
+          <t>381826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>550823</t>
+          <t>546307</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>643813</t>
+          <t>641165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>209751</t>
+          <t>208543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261604</t>
+          <t>258166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>175291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>222161</t>
+          <t>221543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400139</t>
+          <t>396434</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>469152</t>
+          <t>461981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145975</t>
+          <t>147441</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>192224</t>
+          <t>192422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139693</t>
+          <t>138759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182946</t>
+          <t>182329</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>298285</t>
+          <t>297191</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>360127</t>
+          <t>360946</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80494</t>
+          <t>80159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118749</t>
+          <t>116694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103047</t>
+          <t>101828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141374</t>
+          <t>144868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194966</t>
+          <t>195226</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248912</t>
+          <t>250202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>31693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64111</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87897</t>
+          <t>85574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92624</t>
+          <t>93773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137182</t>
+          <t>138531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1153296</t>
+          <t>1152745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1263238</t>
+          <t>1265776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>991373</t>
+          <t>992827</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1100581</t>
+          <t>1096213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2180665</t>
+          <t>2169700</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2344039</t>
+          <t>2328147</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>768037</t>
+          <t>771655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>871091</t>
+          <t>867991</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>720590</t>
+          <t>711408</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>816688</t>
+          <t>812271</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1516489</t>
+          <t>1517257</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1650988</t>
+          <t>1654094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>737779</t>
+          <t>733785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>837523</t>
+          <t>835096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>746428</t>
+          <t>745779</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>852070</t>
+          <t>848774</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1508122</t>
+          <t>1511699</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1655836</t>
+          <t>1647864</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>523684</t>
+          <t>522465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>608559</t>
+          <t>612327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>865827</t>
+          <t>868353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>978388</t>
+          <t>982059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1422166</t>
+          <t>1417239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1556244</t>
+          <t>1561272</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66374</t>
+          <t>86310</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52397</t>
+          <t>69344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82843</t>
+          <t>106314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>56420</t>
+          <t>65253</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>52578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>83110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>122794</t>
+          <t>151562</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104134</t>
+          <t>129951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>179529</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97108</t>
+          <t>110060</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81405</t>
+          <t>93364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116413</t>
+          <t>130661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>102509</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79080</t>
+          <t>89119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>107846</t>
+          <t>119700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>189185</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>189916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211367</t>
+          <t>237773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117187</t>
+          <t>132250</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99496</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137003</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>142029</t>
+          <t>155629</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127928</t>
+          <t>138215</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>158480</t>
+          <t>173168</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>259216</t>
+          <t>287879</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>235302</t>
+          <t>263311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>285021</t>
+          <t>313319</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>229727</t>
+          <t>244969</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>207994</t>
+          <t>220428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251427</t>
+          <t>267069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>455030</t>
+          <t>488081</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>433321</t>
+          <t>465187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>474699</t>
+          <t>511464</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>684756</t>
+          <t>733050</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>656169</t>
+          <t>700950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>721062</t>
+          <t>764253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>510396</t>
+          <t>573589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>745556</t>
+          <t>811472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1255951</t>
+          <t>1385061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>542639</t>
+          <t>581104</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>376724</t>
+          <t>525421</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633755</t>
+          <t>632613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>497443</t>
+          <t>529928</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>369092</t>
+          <t>491631</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>586479</t>
+          <t>572354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1040082</t>
+          <t>1111033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>844851</t>
+          <t>1048354</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1193320</t>
+          <t>1180205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>642856</t>
+          <t>715523</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>433414</t>
+          <t>663798</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>732797</t>
+          <t>768937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>608485</t>
+          <t>617885</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>472030</t>
+          <t>579142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>754887</t>
+          <t>657519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1251341</t>
+          <t>1333408</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1027563</t>
+          <t>1269301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1426576</t>
+          <t>1398041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>475993</t>
+          <t>517291</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>331054</t>
+          <t>475271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555064</t>
+          <t>565543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>665459</t>
+          <t>506467</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>491792</t>
+          <t>472133</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1107664</t>
+          <t>543046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1141452</t>
+          <t>1023758</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>943996</t>
+          <t>968277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1703988</t>
+          <t>1084175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>620057</t>
+          <t>407049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>407640</t>
+          <t>371074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1172065</t>
+          <t>445340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>460709</t>
+          <t>511141</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>336547</t>
+          <t>477577</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>529266</t>
+          <t>546849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1080766</t>
+          <t>918190</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>852994</t>
+          <t>869850</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1632443</t>
+          <t>972622</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2281546</t>
+          <t>2220967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2232096</t>
+          <t>2165420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4513642</t>
+          <t>4386388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>185456</t>
+          <t>204440</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159553</t>
+          <t>178800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>216737</t>
+          <t>232166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>204613</t>
+          <t>226241</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183214</t>
+          <t>204959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>225405</t>
+          <t>249338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>390069</t>
+          <t>430681</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355496</t>
+          <t>395659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>425803</t>
+          <t>467389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>183376</t>
+          <t>205010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159639</t>
+          <t>180089</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>206961</t>
+          <t>230383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>183511</t>
+          <t>199021</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>164129</t>
+          <t>176042</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>205544</t>
+          <t>221207</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>366887</t>
+          <t>404031</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>334587</t>
+          <t>369897</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>396545</t>
+          <t>437850</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>193324</t>
+          <t>208513</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168985</t>
+          <t>183065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>218625</t>
+          <t>236915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>166023</t>
+          <t>183243</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148456</t>
+          <t>162231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187239</t>
+          <t>205163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>359347</t>
+          <t>391755</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>326862</t>
+          <t>360532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>390796</t>
+          <t>427309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82305</t>
+          <t>91171</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66726</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>109989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88902</t>
+          <t>107363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>118685</t>
+          <t>143383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>185747</t>
+          <t>214458</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>164064</t>
+          <t>190507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209578</t>
+          <t>240126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644461</t>
+          <t>709134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657589</t>
+          <t>731791</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1302050</t>
+          <t>1440925</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>794469</t>
+          <t>871854</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>601888</t>
+          <t>814226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>883964</t>
+          <t>937071</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>758476</t>
+          <t>821422</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>634640</t>
+          <t>775557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>843243</t>
+          <t>876911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1552945</t>
+          <t>1693276</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1349960</t>
+          <t>1609088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1694032</t>
+          <t>1769608</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>923341</t>
+          <t>1030594</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>726991</t>
+          <t>969157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1016495</t>
+          <t>1093262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>884072</t>
+          <t>919415</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>738498</t>
+          <t>875686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1029118</t>
+          <t>968350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1807413</t>
+          <t>1950009</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1578559</t>
+          <t>1870491</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1986923</t>
+          <t>2026177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>786504</t>
+          <t>858054</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>634802</t>
+          <t>802357</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>871586</t>
+          <t>911394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>973511</t>
+          <t>845338</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>798766</t>
+          <t>797377</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1474056</t>
+          <t>890107</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1760015</t>
+          <t>1703392</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1563118</t>
+          <t>1640239</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2398753</t>
+          <t>1777673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>932089</t>
+          <t>743189</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>727858</t>
+          <t>696095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1516925</t>
+          <t>792352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1019181</t>
+          <t>1122508</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>844777</t>
+          <t>1074414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1105800</t>
+          <t>1168226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1951270</t>
+          <t>1865697</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1730995</t>
+          <t>1793589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2520879</t>
+          <t>1934735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>26,83%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3436403</t>
+          <t>3503691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3635240</t>
+          <t>3708683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7071643</t>
+          <t>7212374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
